--- a/results/main/Table3_Survival_Performance_ByCohort.xlsx
+++ b/results/main/Table3_Survival_Performance_ByCohort.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">Cohort</t>
   </si>
@@ -38,10 +38,10 @@
     <t xml:space="preserve">C_adj (95%CI)</t>
   </si>
   <si>
-    <t xml:space="preserve">HR multi (CORE-A)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p (multi)</t>
+    <t xml:space="preserve">HR age-adj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p (age-adj)</t>
   </si>
   <si>
     <t xml:space="preserve">TCGA_BRCA</t>
@@ -59,7 +59,10 @@
     <t xml:space="preserve">0.624 (0.572–0.678)</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
+    <t xml:space="preserve">1.27 (1.09–1.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0023</t>
   </si>
   <si>
     <t xml:space="preserve">METABRIC</t>
@@ -77,6 +80,12 @@
     <t xml:space="preserve">0.638 (0.615–0.659)</t>
   </si>
   <si>
+    <t xml:space="preserve">1.41 (1.31–1.53)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07e-19</t>
+  </si>
+  <si>
     <t xml:space="preserve">GSE20685</t>
   </si>
   <si>
@@ -87,6 +96,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.623 (0.562–0.683)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0032</t>
   </si>
 </sst>
 </file>
@@ -472,8 +484,8 @@
     <col min="6" max="6" width="16.145" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="18.7175" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="17.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="9.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="16.145" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,15 +549,15 @@
         <v>15</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>1978</v>
@@ -557,24 +569,24 @@
         <v>159</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>11</v>
@@ -589,19 +601,19 @@
         <v>112.8</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/results/main/Table3_Survival_Performance_ByCohort.xlsx
+++ b/results/main/Table3_Survival_Performance_ByCohort.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">Cohort</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.0032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* HR age-adj: Cox model adjusted for age (CORE-A model). Validation cohorts (TCGA-BRCA, METABRIC, GSE20685): age only. Training cohort (SCANB): age + ER status. ER status not available in processed clinical files for validation cohorts.</t>
   </si>
 </sst>
 </file>
@@ -106,7 +109,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -124,6 +127,12 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5D6D7E"/>
+      <name val="Calibri"/>
+      <i/>
     </font>
   </fonts>
   <fills count="5">
@@ -175,7 +184,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -186,6 +195,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -476,7 +486,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="8.4275" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="203.08" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="8.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="4.14" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
@@ -616,6 +626,11 @@
         <v>28</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/results/main/Table3_Survival_Performance_ByCohort.xlsx
+++ b/results/main/Table3_Survival_Performance_ByCohort.xlsx
@@ -12,11 +12,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
   <si>
     <t xml:space="preserve">Cohort</t>
   </si>
   <si>
+    <t xml:space="preserve">Role</t>
+  </si>
+  <si>
     <t xml:space="preserve">Endpoint</t>
   </si>
   <si>
@@ -44,10 +47,34 @@
     <t xml:space="preserve">p (age-adj)</t>
   </si>
   <si>
+    <t xml:space="preserve">SCANB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92 (1.74–2.13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56e-36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.698 (0.668–0.729)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86 (1.64–2.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41e-21</t>
+  </si>
+  <si>
     <t xml:space="preserve">TCGA_BRCA</t>
   </si>
   <si>
-    <t xml:space="preserve">OS</t>
+    <t xml:space="preserve">Validation</t>
   </si>
   <si>
     <t xml:space="preserve">1.20 (1.04–1.40)</t>
@@ -101,7 +128,7 @@
     <t xml:space="preserve">0.0032</t>
   </si>
   <si>
-    <t xml:space="preserve">* HR age-adj: Cox model adjusted for age (CORE-A model). Validation cohorts (TCGA-BRCA, METABRIC, GSE20685): age only. Training cohort (SCANB): age + ER status. ER status not available in processed clinical files for validation cohorts.</t>
+    <t xml:space="preserve">* Training cohort (SCAN-B): C_adj reported without optimism correction (no cross-validation applied to survival analysis). ** C_adj = max(C_raw, 1 − C_raw); direction-invariant; 95% CI by bootstrap (B=1,000). *** HR age-adj: Cox model adjusted for age only (CORE-A); SCAN-B additionally adjusts for ER status. ER status unavailable in processed clinical files for validation cohorts.</t>
   </si>
 </sst>
 </file>
@@ -486,16 +513,17 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="203.08" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="8.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="4.14" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="6.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="16.145" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="7.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="18.7175" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="16.145" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="11.71" hidden="0" customWidth="1"/>
+    <col min="1" max="1" width="250.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="9.285" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="8.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="4.14" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="6.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.145" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="18.7175" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="16.145" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -529,106 +557,153 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="2" t="n">
-        <v>1072</v>
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>150</v>
+        <v>3069</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
+        <v>322</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>55.7</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="n">
-        <v>1978</v>
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>13</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>646</v>
+        <v>1072</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>159</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>150</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>32</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>1978</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>646</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="n">
         <v>327</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="E5" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="E4" s="2" t="n">
+      <c r="F5" s="3" t="n">
         <v>112.8</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>28</v>
+      <c r="G5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>29</v>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>

--- a/results/main/Table3_Survival_Performance_ByCohort.xlsx
+++ b/results/main/Table3_Survival_Performance_ByCohort.xlsx
@@ -41,10 +41,10 @@
     <t xml:space="preserve">C_adj (95%CI)</t>
   </si>
   <si>
-    <t xml:space="preserve">HR age-adj</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p (age-adj)</t>
+    <t xml:space="preserve">HR adj (CORE-A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p (CORE-A adj)</t>
   </si>
   <si>
     <t xml:space="preserve">SCANB</t>
@@ -107,10 +107,10 @@
     <t xml:space="preserve">0.638 (0.615–0.659)</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41 (1.31–1.53)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07e-19</t>
+    <t xml:space="preserve">1.36 (1.24–1.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82e-12</t>
   </si>
   <si>
     <t xml:space="preserve">GSE20685</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">0.0032</t>
   </si>
   <si>
-    <t xml:space="preserve">* Training cohort (SCAN-B): C_adj reported without optimism correction (no cross-validation applied to survival analysis). ** C_adj = max(C_raw, 1 − C_raw); direction-invariant; 95% CI by bootstrap (B=1,000). *** HR age-adj: Cox model adjusted for age only (CORE-A); SCAN-B additionally adjusts for ER status. ER status unavailable in processed clinical files for validation cohorts.</t>
+    <t xml:space="preserve">* Training cohort (SCAN-B): C_adj = 0.698 (in-sample; no optimism correction). OOF C-index used for model selection = 0.670 (PAM50-full OOF = 0.679; gap = 0.009 &lt; δ = 0.010, non-inferiority confirmed). ** C_adj = max(C_raw, 1 − C_raw); direction-invariant; 95% CI by bootstrap (B=1,000). *** HR adj (CORE-A): Cox model adjusted for available covariates. CORE-A covariates by cohort: SCAN-B (age + ER status), METABRIC (age + ER status), TCGA-BRCA (age only), GSE20685 (age only). Covariates included only if &gt;80% non-missing.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +523,7 @@
     <col min="8" max="8" width="7.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="18.7175" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="16.145" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="11.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="14.71" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
